--- a/exercise/Admin/Admin Penjualan/Tes Excel Admin Penjualan 1.xlsx
+++ b/exercise/Admin/Admin Penjualan/Tes Excel Admin Penjualan 1.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24729"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Documents\Buat Youtube\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Pemrograman\Excel\excel\exercise\Admin\Admin Penjualan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F90A714-6438-4500-91FD-44F693870846}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11310" xr2:uid="{D87DF820-F6BC-44EE-9729-1088ACA7AFEE}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11310"/>
   </bookViews>
   <sheets>
     <sheet name="Tes" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="152511"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -109,7 +108,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="3">
     <numFmt numFmtId="42" formatCode="_-&quot;Rp&quot;* #,##0_-;\-&quot;Rp&quot;* #,##0_-;_-&quot;Rp&quot;* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
@@ -424,7 +423,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="41" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -453,8 +452,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -483,9 +480,9 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="9" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="41" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="41" fontId="3" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="42" fontId="2" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -830,7 +827,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B91A0A0-13AD-42C2-81AB-829C16959F28}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FF002060"/>
   </sheetPr>
@@ -838,7 +835,7 @@
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.5703125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="4.28515625" style="21" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.28515625" style="19" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.140625" style="1" customWidth="1"/>
     <col min="4" max="4" width="14.5703125" style="1" customWidth="1"/>
     <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
@@ -852,59 +849,68 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:11" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B1" s="32" t="s">
+      <c r="B1" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32"/>
-      <c r="H1" s="32"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
+      <c r="H1" s="30"/>
     </row>
     <row r="2" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="23" t="s">
+      <c r="B2" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="24" t="s">
+      <c r="C2" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="D2" s="25" t="s">
+      <c r="D2" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="25" t="s">
+      <c r="E2" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="25" t="s">
+      <c r="F2" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="25" t="s">
+      <c r="G2" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="H2" s="26" t="s">
+      <c r="H2" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="J2" s="31" t="s">
+      <c r="J2" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="K2" s="31"/>
+      <c r="K2" s="29"/>
     </row>
     <row r="3" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="18">
+      <c r="B3" s="16">
         <v>1</v>
       </c>
-      <c r="C3" s="27">
+      <c r="C3" s="25">
         <v>44228</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="28"/>
+      <c r="E3" s="28">
+        <f>VLOOKUP(D3,$J$3:$K$13,2,FALSE)</f>
+        <v>5000000</v>
+      </c>
       <c r="F3" s="13">
         <v>2</v>
       </c>
-      <c r="G3" s="29"/>
-      <c r="H3" s="30"/>
+      <c r="G3" s="26">
+        <f>(E3*F3)*0.05</f>
+        <v>500000</v>
+      </c>
+      <c r="H3" s="27">
+        <f>(E3*F3)+G3</f>
+        <v>10500000</v>
+      </c>
       <c r="J3" s="11" t="s">
         <v>18</v>
       </c>
@@ -913,21 +919,30 @@
       </c>
     </row>
     <row r="4" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B4" s="19">
+      <c r="B4" s="17">
         <v>2</v>
       </c>
-      <c r="C4" s="27">
+      <c r="C4" s="25">
         <v>44229</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="28"/>
+      <c r="E4" s="28">
+        <f t="shared" ref="E4:E12" si="0">VLOOKUP(D4,$J$3:$K$13,2,FALSE)</f>
+        <v>30000</v>
+      </c>
       <c r="F4" s="14">
         <v>20</v>
       </c>
-      <c r="G4" s="29"/>
-      <c r="H4" s="16"/>
+      <c r="G4" s="26">
+        <f t="shared" ref="G4:G12" si="1">(E4*F4)*0.05</f>
+        <v>30000</v>
+      </c>
+      <c r="H4" s="27">
+        <f t="shared" ref="H4:H12" si="2">(E4*F4)+G4</f>
+        <v>630000</v>
+      </c>
       <c r="J4" s="4" t="s">
         <v>8</v>
       </c>
@@ -936,21 +951,30 @@
       </c>
     </row>
     <row r="5" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B5" s="19">
+      <c r="B5" s="17">
         <v>3</v>
       </c>
-      <c r="C5" s="27">
+      <c r="C5" s="25">
         <v>44230</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="E5" s="28"/>
+      <c r="E5" s="28">
+        <f t="shared" si="0"/>
+        <v>1500000</v>
+      </c>
       <c r="F5" s="14">
         <v>3</v>
       </c>
-      <c r="G5" s="29"/>
-      <c r="H5" s="16"/>
+      <c r="G5" s="26">
+        <f t="shared" si="1"/>
+        <v>225000</v>
+      </c>
+      <c r="H5" s="27">
+        <f t="shared" si="2"/>
+        <v>4725000</v>
+      </c>
       <c r="J5" s="5" t="s">
         <v>9</v>
       </c>
@@ -959,21 +983,30 @@
       </c>
     </row>
     <row r="6" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B6" s="19">
+      <c r="B6" s="17">
         <v>4</v>
       </c>
-      <c r="C6" s="27">
+      <c r="C6" s="25">
         <v>44231</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="E6" s="28"/>
+      <c r="E6" s="28">
+        <f t="shared" si="0"/>
+        <v>300000</v>
+      </c>
       <c r="F6" s="14">
         <v>5</v>
       </c>
-      <c r="G6" s="29"/>
-      <c r="H6" s="16"/>
+      <c r="G6" s="26">
+        <f t="shared" si="1"/>
+        <v>75000</v>
+      </c>
+      <c r="H6" s="27">
+        <f t="shared" si="2"/>
+        <v>1575000</v>
+      </c>
       <c r="J6" s="5" t="s">
         <v>10</v>
       </c>
@@ -982,21 +1015,30 @@
       </c>
     </row>
     <row r="7" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B7" s="19">
+      <c r="B7" s="17">
         <v>5</v>
       </c>
-      <c r="C7" s="27">
+      <c r="C7" s="25">
         <v>44232</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="E7" s="28"/>
+      <c r="E7" s="28">
+        <f t="shared" si="0"/>
+        <v>150000</v>
+      </c>
       <c r="F7" s="14">
         <v>10</v>
       </c>
-      <c r="G7" s="29"/>
-      <c r="H7" s="16"/>
+      <c r="G7" s="26">
+        <f t="shared" si="1"/>
+        <v>75000</v>
+      </c>
+      <c r="H7" s="27">
+        <f t="shared" si="2"/>
+        <v>1575000</v>
+      </c>
       <c r="J7" s="5" t="s">
         <v>11</v>
       </c>
@@ -1005,21 +1047,30 @@
       </c>
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B8" s="19">
+      <c r="B8" s="17">
         <v>6</v>
       </c>
-      <c r="C8" s="27">
+      <c r="C8" s="25">
         <v>44233</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E8" s="28"/>
+      <c r="E8" s="28">
+        <f t="shared" si="0"/>
+        <v>30000</v>
+      </c>
       <c r="F8" s="14">
         <v>33</v>
       </c>
-      <c r="G8" s="29"/>
-      <c r="H8" s="16"/>
+      <c r="G8" s="26">
+        <f t="shared" si="1"/>
+        <v>49500</v>
+      </c>
+      <c r="H8" s="27">
+        <f t="shared" si="2"/>
+        <v>1039500</v>
+      </c>
       <c r="J8" s="5" t="s">
         <v>12</v>
       </c>
@@ -1028,21 +1079,30 @@
       </c>
     </row>
     <row r="9" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B9" s="19">
+      <c r="B9" s="17">
         <v>7</v>
       </c>
-      <c r="C9" s="27">
+      <c r="C9" s="25">
         <v>44234</v>
       </c>
       <c r="D9" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E9" s="28"/>
+      <c r="E9" s="28">
+        <f t="shared" si="0"/>
+        <v>5000000</v>
+      </c>
       <c r="F9" s="14">
         <v>1</v>
       </c>
-      <c r="G9" s="29"/>
-      <c r="H9" s="16"/>
+      <c r="G9" s="26">
+        <f t="shared" si="1"/>
+        <v>250000</v>
+      </c>
+      <c r="H9" s="27">
+        <f t="shared" si="2"/>
+        <v>5250000</v>
+      </c>
       <c r="J9" s="5" t="s">
         <v>13</v>
       </c>
@@ -1051,21 +1111,30 @@
       </c>
     </row>
     <row r="10" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B10" s="19">
+      <c r="B10" s="17">
         <v>8</v>
       </c>
-      <c r="C10" s="27">
+      <c r="C10" s="25">
         <v>44235</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="E10" s="28"/>
+      <c r="E10" s="28">
+        <f t="shared" si="0"/>
+        <v>1500000</v>
+      </c>
       <c r="F10" s="14">
         <v>2</v>
       </c>
-      <c r="G10" s="29"/>
-      <c r="H10" s="16"/>
+      <c r="G10" s="26">
+        <f t="shared" si="1"/>
+        <v>150000</v>
+      </c>
+      <c r="H10" s="27">
+        <f t="shared" si="2"/>
+        <v>3150000</v>
+      </c>
       <c r="J10" s="5" t="s">
         <v>14</v>
       </c>
@@ -1074,21 +1143,30 @@
       </c>
     </row>
     <row r="11" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B11" s="19">
+      <c r="B11" s="17">
         <v>9</v>
       </c>
-      <c r="C11" s="27">
+      <c r="C11" s="25">
         <v>44236</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="E11" s="28"/>
+      <c r="E11" s="28">
+        <f t="shared" si="0"/>
+        <v>2500000</v>
+      </c>
       <c r="F11" s="14">
         <v>3</v>
       </c>
-      <c r="G11" s="29"/>
-      <c r="H11" s="16"/>
+      <c r="G11" s="26">
+        <f t="shared" si="1"/>
+        <v>375000</v>
+      </c>
+      <c r="H11" s="27">
+        <f t="shared" si="2"/>
+        <v>7875000</v>
+      </c>
       <c r="J11" s="5" t="s">
         <v>15</v>
       </c>
@@ -1097,21 +1175,30 @@
       </c>
     </row>
     <row r="12" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="20">
+      <c r="B12" s="18">
         <v>10</v>
       </c>
-      <c r="C12" s="27">
+      <c r="C12" s="25">
         <v>44237</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="E12" s="28"/>
+      <c r="E12" s="28">
+        <f t="shared" si="0"/>
+        <v>50000</v>
+      </c>
       <c r="F12" s="15">
         <v>23</v>
       </c>
-      <c r="G12" s="29"/>
-      <c r="H12" s="16"/>
+      <c r="G12" s="26">
+        <f t="shared" si="1"/>
+        <v>57500</v>
+      </c>
+      <c r="H12" s="27">
+        <f t="shared" si="2"/>
+        <v>1207500</v>
+      </c>
       <c r="J12" s="5" t="s">
         <v>16</v>
       </c>
@@ -1120,15 +1207,18 @@
       </c>
     </row>
     <row r="13" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B13" s="33" t="s">
+      <c r="B13" s="31" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="34"/>
-      <c r="D13" s="35"/>
-      <c r="E13" s="35"/>
-      <c r="F13" s="35"/>
-      <c r="G13" s="36"/>
-      <c r="H13" s="17"/>
+      <c r="C13" s="32"/>
+      <c r="D13" s="33"/>
+      <c r="E13" s="33"/>
+      <c r="F13" s="33"/>
+      <c r="G13" s="34"/>
+      <c r="H13" s="27">
+        <f>SUM(H3:H12)</f>
+        <v>37527000</v>
+      </c>
       <c r="J13" s="6" t="s">
         <v>17</v>
       </c>
@@ -1137,19 +1227,19 @@
       </c>
     </row>
     <row r="14" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="C14" s="22"/>
+      <c r="C14" s="20"/>
     </row>
     <row r="15" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B15" s="37" t="s">
+      <c r="B15" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="37"/>
-      <c r="D15" s="37"/>
-      <c r="E15" s="38" t="s">
+      <c r="C15" s="35"/>
+      <c r="D15" s="35"/>
+      <c r="E15" s="36" t="s">
         <v>23</v>
       </c>
-      <c r="F15" s="31"/>
-      <c r="G15" s="31"/>
+      <c r="F15" s="29"/>
+      <c r="G15" s="29"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -1160,7 +1250,7 @@
     <mergeCell ref="E15:G15"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="E15" r:id="rId1" xr:uid="{E6E076C5-1812-415A-8A65-D34C7258DEC1}"/>
+    <hyperlink ref="E15" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId2"/>

--- a/exercise/Admin/Admin Penjualan/Tes Excel Admin Penjualan 1.xlsx
+++ b/exercise/Admin/Admin Penjualan/Tes Excel Admin Penjualan 1.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24729"/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Pemrograman\Excel\excel\exercise\Admin\Admin Penjualan\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Documents\Buat Youtube\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F90A714-6438-4500-91FD-44F693870846}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11310"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11310" xr2:uid="{D87DF820-F6BC-44EE-9729-1088ACA7AFEE}"/>
   </bookViews>
   <sheets>
     <sheet name="Tes" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -108,7 +109,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
     <numFmt numFmtId="42" formatCode="_-&quot;Rp&quot;* #,##0_-;\-&quot;Rp&quot;* #,##0_-;_-&quot;Rp&quot;* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
@@ -423,7 +424,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="41" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -452,6 +453,8 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -480,9 +483,9 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="9" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="41" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="41" fontId="3" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -827,7 +830,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B91A0A0-13AD-42C2-81AB-829C16959F28}">
   <sheetPr>
     <tabColor rgb="FF002060"/>
   </sheetPr>
@@ -835,7 +838,7 @@
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.5703125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="4.28515625" style="19" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.28515625" style="21" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.140625" style="1" customWidth="1"/>
     <col min="4" max="4" width="14.5703125" style="1" customWidth="1"/>
     <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
@@ -849,68 +852,59 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:11" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B1" s="30" t="s">
+      <c r="B1" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="32"/>
     </row>
     <row r="2" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="22" t="s">
+      <c r="C2" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="D2" s="23" t="s">
+      <c r="D2" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="23" t="s">
+      <c r="E2" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="23" t="s">
+      <c r="F2" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="23" t="s">
+      <c r="G2" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="H2" s="24" t="s">
+      <c r="H2" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="J2" s="29" t="s">
+      <c r="J2" s="31" t="s">
         <v>7</v>
       </c>
-      <c r="K2" s="29"/>
+      <c r="K2" s="31"/>
     </row>
     <row r="3" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="16">
+      <c r="B3" s="18">
         <v>1</v>
       </c>
-      <c r="C3" s="25">
+      <c r="C3" s="27">
         <v>44228</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="28">
-        <f>VLOOKUP(D3,$J$3:$K$13,2,FALSE)</f>
-        <v>5000000</v>
-      </c>
+      <c r="E3" s="28"/>
       <c r="F3" s="13">
         <v>2</v>
       </c>
-      <c r="G3" s="26">
-        <f>(E3*F3)*0.05</f>
-        <v>500000</v>
-      </c>
-      <c r="H3" s="27">
-        <f>(E3*F3)+G3</f>
-        <v>10500000</v>
-      </c>
+      <c r="G3" s="29"/>
+      <c r="H3" s="30"/>
       <c r="J3" s="11" t="s">
         <v>18</v>
       </c>
@@ -919,30 +913,21 @@
       </c>
     </row>
     <row r="4" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B4" s="17">
+      <c r="B4" s="19">
         <v>2</v>
       </c>
-      <c r="C4" s="25">
+      <c r="C4" s="27">
         <v>44229</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="28">
-        <f t="shared" ref="E4:E12" si="0">VLOOKUP(D4,$J$3:$K$13,2,FALSE)</f>
-        <v>30000</v>
-      </c>
+      <c r="E4" s="28"/>
       <c r="F4" s="14">
         <v>20</v>
       </c>
-      <c r="G4" s="26">
-        <f t="shared" ref="G4:G12" si="1">(E4*F4)*0.05</f>
-        <v>30000</v>
-      </c>
-      <c r="H4" s="27">
-        <f t="shared" ref="H4:H12" si="2">(E4*F4)+G4</f>
-        <v>630000</v>
-      </c>
+      <c r="G4" s="29"/>
+      <c r="H4" s="16"/>
       <c r="J4" s="4" t="s">
         <v>8</v>
       </c>
@@ -951,30 +936,21 @@
       </c>
     </row>
     <row r="5" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B5" s="17">
+      <c r="B5" s="19">
         <v>3</v>
       </c>
-      <c r="C5" s="25">
+      <c r="C5" s="27">
         <v>44230</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="E5" s="28">
-        <f t="shared" si="0"/>
-        <v>1500000</v>
-      </c>
+      <c r="E5" s="28"/>
       <c r="F5" s="14">
         <v>3</v>
       </c>
-      <c r="G5" s="26">
-        <f t="shared" si="1"/>
-        <v>225000</v>
-      </c>
-      <c r="H5" s="27">
-        <f t="shared" si="2"/>
-        <v>4725000</v>
-      </c>
+      <c r="G5" s="29"/>
+      <c r="H5" s="16"/>
       <c r="J5" s="5" t="s">
         <v>9</v>
       </c>
@@ -983,30 +959,21 @@
       </c>
     </row>
     <row r="6" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B6" s="17">
+      <c r="B6" s="19">
         <v>4</v>
       </c>
-      <c r="C6" s="25">
+      <c r="C6" s="27">
         <v>44231</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="E6" s="28">
-        <f t="shared" si="0"/>
-        <v>300000</v>
-      </c>
+      <c r="E6" s="28"/>
       <c r="F6" s="14">
         <v>5</v>
       </c>
-      <c r="G6" s="26">
-        <f t="shared" si="1"/>
-        <v>75000</v>
-      </c>
-      <c r="H6" s="27">
-        <f t="shared" si="2"/>
-        <v>1575000</v>
-      </c>
+      <c r="G6" s="29"/>
+      <c r="H6" s="16"/>
       <c r="J6" s="5" t="s">
         <v>10</v>
       </c>
@@ -1015,30 +982,21 @@
       </c>
     </row>
     <row r="7" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B7" s="17">
+      <c r="B7" s="19">
         <v>5</v>
       </c>
-      <c r="C7" s="25">
+      <c r="C7" s="27">
         <v>44232</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="E7" s="28">
-        <f t="shared" si="0"/>
-        <v>150000</v>
-      </c>
+      <c r="E7" s="28"/>
       <c r="F7" s="14">
         <v>10</v>
       </c>
-      <c r="G7" s="26">
-        <f t="shared" si="1"/>
-        <v>75000</v>
-      </c>
-      <c r="H7" s="27">
-        <f t="shared" si="2"/>
-        <v>1575000</v>
-      </c>
+      <c r="G7" s="29"/>
+      <c r="H7" s="16"/>
       <c r="J7" s="5" t="s">
         <v>11</v>
       </c>
@@ -1047,30 +1005,21 @@
       </c>
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B8" s="17">
+      <c r="B8" s="19">
         <v>6</v>
       </c>
-      <c r="C8" s="25">
+      <c r="C8" s="27">
         <v>44233</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E8" s="28">
-        <f t="shared" si="0"/>
-        <v>30000</v>
-      </c>
+      <c r="E8" s="28"/>
       <c r="F8" s="14">
         <v>33</v>
       </c>
-      <c r="G8" s="26">
-        <f t="shared" si="1"/>
-        <v>49500</v>
-      </c>
-      <c r="H8" s="27">
-        <f t="shared" si="2"/>
-        <v>1039500</v>
-      </c>
+      <c r="G8" s="29"/>
+      <c r="H8" s="16"/>
       <c r="J8" s="5" t="s">
         <v>12</v>
       </c>
@@ -1079,30 +1028,21 @@
       </c>
     </row>
     <row r="9" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B9" s="17">
+      <c r="B9" s="19">
         <v>7</v>
       </c>
-      <c r="C9" s="25">
+      <c r="C9" s="27">
         <v>44234</v>
       </c>
       <c r="D9" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E9" s="28">
-        <f t="shared" si="0"/>
-        <v>5000000</v>
-      </c>
+      <c r="E9" s="28"/>
       <c r="F9" s="14">
         <v>1</v>
       </c>
-      <c r="G9" s="26">
-        <f t="shared" si="1"/>
-        <v>250000</v>
-      </c>
-      <c r="H9" s="27">
-        <f t="shared" si="2"/>
-        <v>5250000</v>
-      </c>
+      <c r="G9" s="29"/>
+      <c r="H9" s="16"/>
       <c r="J9" s="5" t="s">
         <v>13</v>
       </c>
@@ -1111,30 +1051,21 @@
       </c>
     </row>
     <row r="10" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B10" s="17">
+      <c r="B10" s="19">
         <v>8</v>
       </c>
-      <c r="C10" s="25">
+      <c r="C10" s="27">
         <v>44235</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="E10" s="28">
-        <f t="shared" si="0"/>
-        <v>1500000</v>
-      </c>
+      <c r="E10" s="28"/>
       <c r="F10" s="14">
         <v>2</v>
       </c>
-      <c r="G10" s="26">
-        <f t="shared" si="1"/>
-        <v>150000</v>
-      </c>
-      <c r="H10" s="27">
-        <f t="shared" si="2"/>
-        <v>3150000</v>
-      </c>
+      <c r="G10" s="29"/>
+      <c r="H10" s="16"/>
       <c r="J10" s="5" t="s">
         <v>14</v>
       </c>
@@ -1143,30 +1074,21 @@
       </c>
     </row>
     <row r="11" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B11" s="17">
+      <c r="B11" s="19">
         <v>9</v>
       </c>
-      <c r="C11" s="25">
+      <c r="C11" s="27">
         <v>44236</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="E11" s="28">
-        <f t="shared" si="0"/>
-        <v>2500000</v>
-      </c>
+      <c r="E11" s="28"/>
       <c r="F11" s="14">
         <v>3</v>
       </c>
-      <c r="G11" s="26">
-        <f t="shared" si="1"/>
-        <v>375000</v>
-      </c>
-      <c r="H11" s="27">
-        <f t="shared" si="2"/>
-        <v>7875000</v>
-      </c>
+      <c r="G11" s="29"/>
+      <c r="H11" s="16"/>
       <c r="J11" s="5" t="s">
         <v>15</v>
       </c>
@@ -1175,30 +1097,21 @@
       </c>
     </row>
     <row r="12" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="18">
+      <c r="B12" s="20">
         <v>10</v>
       </c>
-      <c r="C12" s="25">
+      <c r="C12" s="27">
         <v>44237</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="E12" s="28">
-        <f t="shared" si="0"/>
-        <v>50000</v>
-      </c>
+      <c r="E12" s="28"/>
       <c r="F12" s="15">
         <v>23</v>
       </c>
-      <c r="G12" s="26">
-        <f t="shared" si="1"/>
-        <v>57500</v>
-      </c>
-      <c r="H12" s="27">
-        <f t="shared" si="2"/>
-        <v>1207500</v>
-      </c>
+      <c r="G12" s="29"/>
+      <c r="H12" s="16"/>
       <c r="J12" s="5" t="s">
         <v>16</v>
       </c>
@@ -1207,18 +1120,15 @@
       </c>
     </row>
     <row r="13" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B13" s="31" t="s">
+      <c r="B13" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="32"/>
-      <c r="D13" s="33"/>
-      <c r="E13" s="33"/>
-      <c r="F13" s="33"/>
-      <c r="G13" s="34"/>
-      <c r="H13" s="27">
-        <f>SUM(H3:H12)</f>
-        <v>37527000</v>
-      </c>
+      <c r="C13" s="34"/>
+      <c r="D13" s="35"/>
+      <c r="E13" s="35"/>
+      <c r="F13" s="35"/>
+      <c r="G13" s="36"/>
+      <c r="H13" s="17"/>
       <c r="J13" s="6" t="s">
         <v>17</v>
       </c>
@@ -1227,19 +1137,19 @@
       </c>
     </row>
     <row r="14" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="C14" s="20"/>
+      <c r="C14" s="22"/>
     </row>
     <row r="15" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B15" s="35" t="s">
+      <c r="B15" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="35"/>
-      <c r="D15" s="35"/>
-      <c r="E15" s="36" t="s">
+      <c r="C15" s="37"/>
+      <c r="D15" s="37"/>
+      <c r="E15" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="F15" s="29"/>
-      <c r="G15" s="29"/>
+      <c r="F15" s="31"/>
+      <c r="G15" s="31"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -1250,7 +1160,7 @@
     <mergeCell ref="E15:G15"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="E15" r:id="rId1"/>
+    <hyperlink ref="E15" r:id="rId1" xr:uid="{E6E076C5-1812-415A-8A65-D34C7258DEC1}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId2"/>
